--- a/docs/validation/V15_Coefficients_Carry_Their_Sample.xlsx
+++ b/docs/validation/V15_Coefficients_Carry_Their_Sample.xlsx
@@ -1090,7 +1090,7 @@
       </c>
       <c r="B39" s="14" t="inlineStr">
         <is>
-          <t>Double-click the R2 file — the R2 file. Power BI Desktop opens it and shows the first report page.</t>
+          <t>Double-click the R2 file — R2_Consumer_Stress.pbip. Power BI Desktop opens it and shows the first report page.</t>
         </is>
       </c>
     </row>

--- a/docs/validation/V15_Coefficients_Carry_Their_Sample.xlsx
+++ b/docs/validation/V15_Coefficients_Carry_Their_Sample.xlsx
@@ -2112,7 +2112,7 @@
   </conditionalFormatting>
   <dataValidations count="1">
     <dataValidation sqref="F50:F54" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Pass,Fail,N/A"</formula1>
+      <formula1>"Pass,Fail,N/A,Not run"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
